--- a/projects/KE_Kapiti_Eddy_July/KE_Kapiti_output_eddy/Kapiti.Biomass.Clippings.xlsx
+++ b/projects/KE_Kapiti_Eddy_July/KE_Kapiti_output_eddy/Kapiti.Biomass.Clippings.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\Soil.C.modelling\Kapiti.soil.C\projects\KE_Kapiti_Eddy_July\KE_Kapiti_output_eddy\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9D14AF-820B-4CE4-8E51-FB2A6B872176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{F9685192-7F5D-44C7-BE52-AE5DC9386920}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="3" activeTab="6" xr2:uid="{F9685192-7F5D-44C7-BE52-AE5DC9386920}"/>
   </bookViews>
   <sheets>
     <sheet name="KAPITI_BIOMASS_CAGES_RAW_REVD" sheetId="6" r:id="rId1"/>
@@ -3618,7 +3618,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H45" si="1">IF(OR(G3=3,G3=4,G3=5,G3=6,G3=11,G3=12),1,0)</f>
+        <f t="shared" ref="H3" si="1">IF(OR(G3=3,G3=4,G3=5,G3=6,G3=11,G3=12),1,0)</f>
         <v>0</v>
       </c>
       <c r="I3" s="1"/>
